--- a/business_forms/039_startup_launch_checklist_form--business_forms.xlsx
+++ b/business_forms/039_startup_launch_checklist_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reported Date</t>
+          <t>Business Launch Reported Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Launch Dateistency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Items Launch Dateistency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Items Launch Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Launch Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_launch_date_time</t>
+          <t>business_launch_checklist_page_launch_date_time_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Launch Date and Time</t>
+          <t>Business Launch Checklist Page Launch Date Time 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_launch_date</t>
+          <t>business_launch_checklist_page_launch_date_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Launch Date 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Business Launch Checklist Page Launch</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_items_launch_date</t>
+          <t>business_launch_checklist_page_items_launch_date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Items Launch Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_items</t>
+          <t>business_launch_checklist_page_items_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_items_launch_date</t>
+          <t>business_launch_checklist_page_items_launch_date_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Items Launch Date 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_items_launch_date</t>
+          <t>business_launch_checklist_page_items_launch_date_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Items Launch Date 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_launch_date</t>
+          <t>business_launch_checklist_page_launch_date_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Launch Date</t>
+          <t>Business Launch Checklist Page Launch Date 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>business_launch_reported_date</t>
+          <t>business_launch_reported_date_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reported Date</t>
+          <t>Business Launch Reported Date 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_items_launch</t>
+          <t>business_launch_checklist_page_items_launch_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Launch</t>
+          <t>Business Launch Checklist Page Items Launch 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reported Date</t>
+          <t>Business Launch Checklist Reported Date</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_items_choices</t>
+          <t>business_launch_checklist_page_items_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>business_launch_checklist_page_items_choices</t>
+          <t>business_launch_checklist_page_items_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
